--- a/dataset/construct/dataset_splits/data_size/5_percent/lmu/fold1.xlsx
+++ b/dataset/construct/dataset_splits/data_size/5_percent/lmu/fold1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54617532</v>
+        <v>51253128</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,77 +625,83 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>88.7994524298426</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>83.41683778234091</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.0636451647603</v>
+      </c>
       <c r="E2" t="n">
-        <v>24.1632653061225</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>31</v>
+      </c>
       <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>588</v>
+      </c>
+      <c r="M2" t="n">
+        <v>169</v>
+      </c>
+      <c r="N2" t="n">
+        <v>564</v>
+      </c>
       <c r="O2" t="n">
-        <v>199</v>
+        <v>1321</v>
       </c>
       <c r="P2" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>647</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>27.53380515489789</v>
       </c>
       <c r="X2" t="n">
-        <v>27.7</v>
+        <v>27.05287582335326</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>90.7</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>620.8</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -725,24 +716,15 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>235</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>172</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54278598</v>
+        <v>54267454</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -750,65 +732,71 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>87.33470225872691</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>83.6002737850787</v>
+      </c>
+      <c r="D3" t="n">
+        <v>31.1845871246102</v>
+      </c>
       <c r="E3" t="n">
-        <v>20.956607495069</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>60</v>
+      </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>53</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>84</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
       <c r="O3" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="P3" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>20.1</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>20.62648062470964</v>
       </c>
       <c r="X3" t="n">
-        <v>21.7</v>
+        <v>20.10605768054529</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>70.3</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>379.3</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -832,27 +820,18 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>184</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54406706</v>
+        <v>51517324</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -860,71 +839,85 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>81.79603011635869</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>85.9247091033539</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24.1287923737194</v>
+      </c>
       <c r="E4" t="n">
-        <v>23.0300453514739</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>60</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>68</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>615</v>
+      </c>
+      <c r="I4" t="n">
+        <v>358</v>
+      </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>454</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1427</v>
+      </c>
+      <c r="L4" t="n">
+        <v>608</v>
+      </c>
+      <c r="M4" t="n">
+        <v>312</v>
+      </c>
+      <c r="N4" t="n">
+        <v>454</v>
+      </c>
       <c r="O4" t="n">
-        <v>197</v>
+        <v>1374</v>
       </c>
       <c r="P4" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>513</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>27.66112910937141</v>
       </c>
       <c r="X4" t="n">
-        <v>23.9</v>
+        <v>27.07404672198142</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>78.2</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>465.2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -936,33 +929,24 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>51409719</v>
+        <v>54391258</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -970,86 +954,80 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>76.2765229295003</v>
+        <v>83.09377138945931</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>23.5078053259871</v>
       </c>
       <c r="E5" t="n">
-        <v>29.3523545006944</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>63</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>527</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>702</v>
+        <v>131</v>
       </c>
       <c r="M5" t="n">
-        <v>676</v>
+        <v>30</v>
       </c>
       <c r="N5" t="n">
-        <v>1905</v>
+        <v>244</v>
       </c>
       <c r="O5" t="n">
-        <v>485</v>
+        <v>405</v>
       </c>
       <c r="P5" t="n">
-        <v>252</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>702</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1438</v>
+        <v>29</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>27.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>27.69296009798979</v>
       </c>
       <c r="X5" t="n">
-        <v>25.9</v>
+        <v>27.05758189903005</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>84.7</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>537.1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1058,33 +1036,24 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>235</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>151</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>51961920</v>
+        <v>52781527</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1092,84 +1061,80 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>85.864476386037</v>
+        <v>75.1485284052019</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>22.0317256849864</v>
       </c>
       <c r="E6" t="n">
-        <v>23.5555555555556</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>456</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>379</v>
+        <v>179.56747</v>
       </c>
       <c r="M6" t="n">
-        <v>506</v>
+        <v>114.70169</v>
       </c>
       <c r="N6" t="n">
-        <v>1341</v>
+        <v>276.0751</v>
       </c>
       <c r="O6" t="n">
-        <v>392</v>
+        <v>570.3442600000001</v>
       </c>
       <c r="P6" t="n">
-        <v>352</v>
+        <v>86</v>
       </c>
       <c r="Q6" t="n">
-        <v>506</v>
+        <v>45</v>
       </c>
       <c r="R6" t="n">
-        <v>1250</v>
+        <v>188</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>571</v>
+        <v>24.394547</v>
       </c>
       <c r="V6" t="n">
-        <v>571</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>24.33657970031115</v>
       </c>
       <c r="X6" t="n">
-        <v>26.8</v>
+        <v>23.89775321488971</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>534.4</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1178,29 +1143,24 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+        <v>152</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>52496143</v>
+        <v>54549554</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1208,82 +1168,80 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86.07802874743329</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>73.8562628336756</v>
+      </c>
+      <c r="D7" t="n">
+        <v>26.7036235803137</v>
+      </c>
       <c r="E7" t="n">
-        <v>23.1206235962478</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>58</v>
+      </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>60</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>298</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>45</v>
+        <v>720</v>
       </c>
       <c r="M7" t="n">
-        <v>93</v>
+        <v>351</v>
       </c>
       <c r="N7" t="n">
-        <v>437</v>
+        <v>246</v>
       </c>
       <c r="O7" t="n">
-        <v>290</v>
+        <v>1317</v>
       </c>
       <c r="P7" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="Q7" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>428</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>26.6107064849649</v>
       </c>
       <c r="X7" t="n">
-        <v>30.1</v>
+        <v>25.8297797404706</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>100.9</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>731.2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1292,27 +1250,18 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>166</v>
-      </c>
-      <c r="AN7" t="n">
         <v>152</v>
       </c>
     </row>
